--- a/data/Alcohol_Dataset_Cleaned.xlsx
+++ b/data/Alcohol_Dataset_Cleaned.xlsx
@@ -1131,30 +1131,76 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>24% vs 27% good adjustment (LSD+HRTL vs control, combined)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Chi-squared</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>chi-square = 1.408</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>&gt;0.05</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q4" t="n">
-        <v>81</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+        <v>158</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
       <c r="T4" t="n">
-        <v>93</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Severe</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>30-50</t>
@@ -1164,41 +1210,95 @@
         <v>0</v>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM4" t="n">
         <v>12</v>
       </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/data/Alcohol_Dataset_Cleaned.xlsx
+++ b/data/Alcohol_Dataset_Cleaned.xlsx
@@ -933,7 +933,7 @@
         <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1377,13 +1377,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>NNT = 4 (modeled); F(1, 797) = 25.1 for time-by-treatment interaction</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.219</v>
+        <v>0.14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1914,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>62.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2148,7 +2148,11 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
@@ -2162,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -2192,7 +2196,7 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -2376,7 +2380,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>F2,52 = 6.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2394,7 +2398,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2436,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -2477,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2660,7 +2664,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2939,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>95</v>
@@ -3175,7 +3179,11 @@
       <c r="H11" t="n">
         <v>8.5</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>NS</t>
@@ -3954,7 +3962,11 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Non-significant (no statistic)</t>
@@ -3982,7 +3994,11 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
@@ -4449,10 +4465,14 @@
       <c r="H16" t="n">
         <v>-44</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>95% CI = [-82% to -5.9%]</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.043</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -4706,7 +4726,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>46/61 (75.4%) alcoholics much improved or improved</t>
+          <t>49% much improved (alcoholics), 52% much improved (composite)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5275,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>91.09999999999999</v>
@@ -5327,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -5338,7 +5358,11 @@
       <c r="AK19" t="n">
         <v>0</v>
       </c>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AM19" t="n">
         <v>1</v>
       </c>
@@ -5405,7 +5429,7 @@
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -6019,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>88.40000000000001</v>
@@ -6082,7 +6106,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AM22" t="n">
@@ -6092,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP22" t="n">
         <v>0</v>
@@ -6231,8 +6255,16 @@
           <t>53 vs 33</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>F = 4.43</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
+      </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
@@ -6487,7 +6519,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>95% CI: psilocybin 14.31-19.29 days; placebo 10.97-16.63 days (abstinence-duration means paired with Cohen's d in Abstract)</t>
+          <t>SD = 10.71</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -6755,7 +6787,11 @@
       <c r="H25" t="n">
         <v>2.98</v>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>χ2 = 4.133 (log-rank test, time to relapse)</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>&lt;0.05</t>
@@ -6785,7 +6821,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>100</v>
@@ -6857,7 +6893,7 @@
         <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -7579,10 +7615,10 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
@@ -7591,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
@@ -7633,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -7668,7 +7704,7 @@
         <v>1</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
@@ -8068,7 +8104,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>RR = 0.37 (KET vs LA), RR = 0.52 (NTX vs LA)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8102,7 +8138,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -8162,7 +8198,7 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
         <v>1</v>
@@ -8352,7 +8388,11 @@
           <t>95% Credible Interval = 0.40–0.85</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.423</t>
+        </is>
+      </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
@@ -8458,7 +8498,7 @@
         <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
         <v>1</v>
@@ -8594,7 +8634,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>44% vs 11%</t>
+          <t>χ² = 7.19 (LSD vs control I, nonschiz, abstinence at 1yr); χ² = 2.25 vs control II (NS)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">

--- a/data/Alcohol_Dataset_Cleaned.xlsx
+++ b/data/Alcohol_Dataset_Cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV33"/>
+  <dimension ref="A1:BW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,70 +719,75 @@
       </c>
       <c r="BI1" t="inlineStr">
         <is>
+          <t>BaseStatusReportedYN</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
           <t>SafetyReported</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>AnyAEReported</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>NumDistinctAEs</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>NParticipantsWithAE</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>AE_denominator</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>ArmScope</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>WorstSeverity</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>text_source</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>text_format</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>PromptVersion</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>RubricVersion</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>SourcePDF</t>
         </is>
@@ -995,64 +1000,69 @@
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr">
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW2" t="inlineStr">
         <is>
           <t>alcohol/Psilocybin-assisted treatment for alcohol dependence - A proof-of-concept study (Bogenschutz et al., 2015) (1).pdf</t>
         </is>
@@ -1265,64 +1275,69 @@
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr">
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW3" t="inlineStr">
         <is>
           <t>alcohol/jamapsychiatry_bogenschutz_2022_oi_220046_1664208846.29988 (1).pdf</t>
         </is>
@@ -1529,44 +1544,49 @@
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr">
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>OCR</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW4" t="inlineStr">
         <is>
           <t>alcohol/Bowen, W. T., Soskin, R. A., &amp; Chotlos, J. W. (1970) Lysergic acid diethylamide.pdf</t>
         </is>
@@ -1779,64 +1799,69 @@
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr">
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW5" t="inlineStr">
         <is>
           <t>alcohol/dakwar-et-al-2019-a-single-ketamine-infusion-combined-with-motivational-enhancement-therapy-for-alcohol-use-disorder-a (1).pdf</t>
         </is>
@@ -2047,44 +2072,49 @@
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr">
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW6" t="inlineStr">
         <is>
           <t>alcohol/s41467-019-13162-w.pdf</t>
         </is>
@@ -2289,68 +2319,73 @@
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW7" t="inlineStr">
         <is>
           <t>alcohol/qjsa.1967.28.295.pdf</t>
         </is>
@@ -2563,44 +2598,49 @@
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr">
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW8" t="inlineStr">
         <is>
           <t>alcohol/10.1177_02698811241254834.pdf</t>
         </is>
@@ -2807,68 +2847,73 @@
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW9" t="inlineStr">
         <is>
           <t>alcohol/grabski-et-al-2022-adjunctive-ketamine-with-relapse-prevention-based-psychological-therapy-in-the-treatment-of-alcohol (1).pdf</t>
         </is>
@@ -3081,64 +3126,69 @@
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr">
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW10" t="inlineStr">
         <is>
           <t>alcohol/Heinzerling, K. G., Sergi,. Nature-themed video intervention.pdf</t>
         </is>
@@ -3345,64 +3395,69 @@
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr">
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>OCR</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW11" t="inlineStr">
         <is>
           <t>alcohol/Hollister, L. E., Shelton, J., &amp; Krieger, G. (1969). A controlled comparison of lysergic acid diethylamide (LSD).pdf</t>
         </is>
@@ -3609,64 +3664,69 @@
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr">
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW12" t="inlineStr">
         <is>
           <t>alcohol/Jensen, S. E., &amp; Ramsay, R. (1963). Treatment of chronic alcoholism with lysergic acid diethylamide.pdf</t>
         </is>
@@ -3877,64 +3937,69 @@
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BK13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BL13" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr">
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BQ13" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BR13" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BS13" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
+      <c r="BT13" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BU13" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV13" t="inlineStr">
+      <c r="BV13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW13" t="inlineStr">
         <is>
           <t>alcohol/v1_covered_0fc93b81-dfaa-4726-85f8-e5a38067a1dc (1).pdf</t>
         </is>
@@ -4135,44 +4200,49 @@
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr"/>
       <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr"/>
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr"/>
       <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr">
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ14" t="inlineStr">
+      <c r="BR14" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR14" t="inlineStr">
+      <c r="BS14" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS14" t="inlineStr">
+      <c r="BT14" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT14" t="inlineStr">
+      <c r="BU14" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV14" t="inlineStr">
+      <c r="BV14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW14" t="inlineStr">
         <is>
           <t>alcohol/Johnson, F. G. (1969). LSD in the treatment of alcoholism.pdf</t>
         </is>
@@ -4367,64 +4437,69 @@
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="BK15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BK15" t="inlineStr">
+      <c r="BL15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BL15" t="inlineStr">
+      <c r="BM15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BM15" t="inlineStr">
+      <c r="BN15" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="BO15" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr">
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ15" t="inlineStr">
+      <c r="BR15" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR15" t="inlineStr">
+      <c r="BS15" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS15" t="inlineStr">
+      <c r="BT15" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT15" t="inlineStr">
+      <c r="BU15" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV15" t="inlineStr">
+      <c r="BV15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW15" t="inlineStr">
         <is>
           <t>alcohol/Kurland, A. A., Unger, S., Shaffer, J. W., &amp; Savage, C. (1967). Psychedelic therapy utilizing LSD in the treatment of the alcoholic patient_ a pre.pdf</t>
         </is>
@@ -4635,68 +4710,73 @@
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="BK16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK16" t="inlineStr">
+      <c r="BL16" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BL16" t="inlineStr">
+      <c r="BM16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="BM16" t="inlineStr">
+      <c r="BN16" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="BO16" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr">
+      <c r="BQ16" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ16" t="inlineStr">
+      <c r="BR16" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR16" t="inlineStr">
+      <c r="BS16" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS16" t="inlineStr">
+      <c r="BT16" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT16" t="inlineStr">
+      <c r="BU16" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV16" t="inlineStr">
+      <c r="BV16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW16" t="inlineStr">
         <is>
           <t>alcohol/Addiction - 2025 - Luquiens - Psilocybin in alcohol use disorder and comorbid depressive symptoms  Results from a.pdf</t>
         </is>
@@ -4897,64 +4977,69 @@
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
+      <c r="BK17" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK17" t="inlineStr">
+      <c r="BL17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BL17" t="inlineStr"/>
-      <c r="BM17" t="inlineStr">
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="BO17" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO17" t="inlineStr">
+      <c r="BP17" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="BP17" t="inlineStr">
+      <c r="BQ17" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ17" t="inlineStr">
+      <c r="BR17" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR17" t="inlineStr">
+      <c r="BS17" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS17" t="inlineStr">
+      <c r="BT17" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT17" t="inlineStr">
+      <c r="BU17" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV17" t="inlineStr">
+      <c r="BV17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW17" t="inlineStr">
         <is>
           <t>alcohol/MacLean, J. R., MacDonald, D. C., Byrne, U. P., &amp; Hubbard, A. M. (196. The use of LSD-25 in the treatment of alcoholism and other psychiatric problems.pdf</t>
         </is>
@@ -5163,64 +5248,69 @@
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="BK18" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BK18" t="inlineStr">
+      <c r="BL18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BL18" t="inlineStr">
+      <c r="BM18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BM18" t="inlineStr">
+      <c r="BN18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="BO18" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr">
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ18" t="inlineStr">
+      <c r="BR18" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR18" t="inlineStr">
+      <c r="BS18" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS18" t="inlineStr">
+      <c r="BT18" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT18" t="inlineStr">
+      <c r="BU18" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV18" t="inlineStr">
+      <c r="BV18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW18" t="inlineStr">
         <is>
           <t>alcohol/Marva. Ketamine Therapy in Patients of Alcohol Use Disorder_ A Prospective Pilot Study to Evaluate Abstinence Rate with This Add-on Treatment Modality.pdf</t>
         </is>
@@ -5429,44 +5519,49 @@
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr"/>
       <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr"/>
       <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr"/>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr">
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ19" t="inlineStr">
+      <c r="BR19" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR19" t="inlineStr">
+      <c r="BS19" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS19" t="inlineStr">
+      <c r="BT19" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT19" t="inlineStr">
+      <c r="BU19" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV19" t="inlineStr">
+      <c r="BV19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW19" t="inlineStr">
         <is>
           <t>alcohol/1-s2.0-S037687162200093X-main (1).pdf</t>
         </is>
@@ -5671,64 +5766,69 @@
       <c r="BH20" t="inlineStr"/>
       <c r="BI20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
+      <c r="BK20" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK20" t="inlineStr">
+      <c r="BL20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BL20" t="inlineStr"/>
-      <c r="BM20" t="inlineStr">
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="BN20" t="inlineStr">
+      <c r="BO20" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO20" t="inlineStr">
+      <c r="BP20" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP20" t="inlineStr">
+      <c r="BQ20" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ20" t="inlineStr">
+      <c r="BR20" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR20" t="inlineStr">
+      <c r="BS20" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS20" t="inlineStr">
+      <c r="BT20" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT20" t="inlineStr">
+      <c r="BU20" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV20" t="inlineStr">
+      <c r="BV20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW20" t="inlineStr">
         <is>
           <t>alcohol/o-reilly-funk-1964-lsd-in-chronic-alcoholism.pdf</t>
         </is>
@@ -5931,44 +6031,49 @@
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BJ21" t="inlineStr"/>
       <c r="BK21" t="inlineStr"/>
       <c r="BL21" t="inlineStr"/>
       <c r="BM21" t="inlineStr"/>
       <c r="BN21" t="inlineStr"/>
       <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr">
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ21" t="inlineStr">
+      <c r="BR21" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR21" t="inlineStr">
+      <c r="BS21" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS21" t="inlineStr">
+      <c r="BT21" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT21" t="inlineStr">
+      <c r="BU21" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV21" t="inlineStr">
+      <c r="BV21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW21" t="inlineStr">
         <is>
           <t>alcohol/s41598-024-52967-8.pdf</t>
         </is>
@@ -6175,44 +6280,49 @@
       <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BJ22" t="inlineStr"/>
       <c r="BK22" t="inlineStr"/>
       <c r="BL22" t="inlineStr"/>
       <c r="BM22" t="inlineStr"/>
       <c r="BN22" t="inlineStr"/>
       <c r="BO22" t="inlineStr"/>
-      <c r="BP22" t="inlineStr">
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ22" t="inlineStr">
+      <c r="BR22" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR22" t="inlineStr">
+      <c r="BS22" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS22" t="inlineStr">
+      <c r="BT22" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT22" t="inlineStr">
+      <c r="BU22" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV22" t="inlineStr">
+      <c r="BV22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW22" t="inlineStr">
         <is>
           <t>alcohol/pagni-et-al-2025-multidimensional-personality-changes-following-psilocybin-assisted-therapy-in-patients-with-alcohol (1).pdf</t>
         </is>
@@ -6415,68 +6525,73 @@
       <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ23" t="inlineStr">
+      <c r="BK23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK23" t="inlineStr">
+      <c r="BL23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BL23" t="inlineStr">
+      <c r="BM23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="BM23" t="inlineStr">
+      <c r="BN23" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BN23" t="inlineStr">
+      <c r="BO23" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO23" t="inlineStr">
+      <c r="BP23" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="BP23" t="inlineStr">
+      <c r="BQ23" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ23" t="inlineStr">
+      <c r="BR23" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR23" t="inlineStr">
+      <c r="BS23" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS23" t="inlineStr">
+      <c r="BT23" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT23" t="inlineStr">
+      <c r="BU23" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV23" t="inlineStr">
+      <c r="BV23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW23" t="inlineStr">
         <is>
           <t>alcohol/Pahnke, W. N., Kurland, A. A., Unger, S., Savage, C., &amp; Grof, S. (1970). The experimental use of psychedelic (LSD) psychotherapy.pdf</t>
         </is>
@@ -6689,64 +6804,69 @@
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ24" t="inlineStr">
+      <c r="BK24" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK24" t="inlineStr">
+      <c r="BL24" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BL24" t="inlineStr"/>
-      <c r="BM24" t="inlineStr">
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="BN24" t="inlineStr">
+      <c r="BO24" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO24" t="inlineStr">
+      <c r="BP24" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP24" t="inlineStr">
+      <c r="BQ24" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ24" t="inlineStr">
+      <c r="BR24" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR24" t="inlineStr">
+      <c r="BS24" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS24" t="inlineStr">
+      <c r="BT24" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT24" t="inlineStr">
+      <c r="BU24" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU24" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV24" t="inlineStr">
+      <c r="BV24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW24" t="inlineStr">
         <is>
           <t>alcohol/1-s2.0-S2589537025000811-main (1).pdf</t>
         </is>
@@ -6955,64 +7075,69 @@
       <c r="BH25" t="inlineStr"/>
       <c r="BI25" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ25" t="inlineStr">
+      <c r="BK25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BK25" t="inlineStr">
+      <c r="BL25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BL25" t="inlineStr">
+      <c r="BM25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BM25" t="inlineStr">
+      <c r="BN25" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="BN25" t="inlineStr">
+      <c r="BO25" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO25" t="inlineStr"/>
-      <c r="BP25" t="inlineStr">
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ25" t="inlineStr">
+      <c r="BR25" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR25" t="inlineStr">
+      <c r="BS25" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS25" t="inlineStr">
+      <c r="BT25" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT25" t="inlineStr">
+      <c r="BU25" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV25" t="inlineStr">
+      <c r="BV25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW25" t="inlineStr">
         <is>
           <t>alcohol/115d425e-5129-48c5-8c21-e1af10229ed5 (1).pdf</t>
         </is>
@@ -7217,68 +7342,73 @@
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ26" t="inlineStr">
+      <c r="BK26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK26" t="inlineStr">
+      <c r="BL26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="BL26" t="inlineStr">
+      <c r="BM26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BM26" t="inlineStr">
+      <c r="BN26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BN26" t="inlineStr">
+      <c r="BO26" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO26" t="inlineStr">
+      <c r="BP26" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP26" t="inlineStr">
+      <c r="BQ26" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ26" t="inlineStr">
+      <c r="BR26" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR26" t="inlineStr">
+      <c r="BS26" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS26" t="inlineStr">
+      <c r="BT26" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT26" t="inlineStr">
+      <c r="BU26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU26" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV26" t="inlineStr">
+      <c r="BV26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW26" t="inlineStr">
         <is>
           <t>alcohol/bcr-2019-230109 (1).pdf</t>
         </is>
@@ -7481,64 +7611,69 @@
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ27" t="inlineStr">
+      <c r="BK27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK27" t="inlineStr">
+      <c r="BL27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BL27" t="inlineStr"/>
-      <c r="BM27" t="inlineStr">
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="BN27" t="inlineStr">
+      <c r="BO27" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO27" t="inlineStr">
+      <c r="BP27" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP27" t="inlineStr">
+      <c r="BQ27" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ27" t="inlineStr">
+      <c r="BR27" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR27" t="inlineStr">
+      <c r="BS27" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS27" t="inlineStr">
+      <c r="BT27" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT27" t="inlineStr">
+      <c r="BU27" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU27" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV27" t="inlineStr">
+      <c r="BV27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW27" t="inlineStr">
         <is>
           <t>alcohol/BIMA_Paper_for_Pure (1).pdf</t>
         </is>
@@ -7751,68 +7886,73 @@
       <c r="BH28" t="inlineStr"/>
       <c r="BI28" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ28" t="inlineStr">
+      <c r="BK28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK28" t="inlineStr">
+      <c r="BL28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BL28" t="inlineStr">
+      <c r="BM28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="BM28" t="inlineStr">
+      <c r="BN28" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="BN28" t="inlineStr">
+      <c r="BO28" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO28" t="inlineStr">
+      <c r="BP28" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP28" t="inlineStr">
+      <c r="BQ28" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ28" t="inlineStr">
+      <c r="BR28" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR28" t="inlineStr">
+      <c r="BS28" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS28" t="inlineStr">
+      <c r="BT28" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT28" t="inlineStr">
+      <c r="BU28" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV28" t="inlineStr">
+      <c r="BV28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW28" t="inlineStr">
         <is>
           <t>alcohol/1966_smart_4543_1 (1).pdf</t>
         </is>
@@ -8017,64 +8157,69 @@
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ29" t="inlineStr">
+      <c r="BK29" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK29" t="inlineStr">
+      <c r="BL29" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="BL29" t="inlineStr"/>
-      <c r="BM29" t="inlineStr">
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="BN29" t="inlineStr">
+      <c r="BO29" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO29" t="inlineStr">
+      <c r="BP29" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="BP29" t="inlineStr">
+      <c r="BQ29" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ29" t="inlineStr">
+      <c r="BR29" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR29" t="inlineStr">
+      <c r="BS29" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS29" t="inlineStr">
+      <c r="BT29" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT29" t="inlineStr">
+      <c r="BU29" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV29" t="inlineStr">
+      <c r="BV29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW29" t="inlineStr">
         <is>
           <t>alcohol/Smith, C. M. (1958). A new adjunct to the treatment of alcoholism The hallucinogenic drugs.pdf</t>
         </is>
@@ -8283,64 +8428,69 @@
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ30" t="inlineStr">
+      <c r="BK30" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK30" t="inlineStr">
+      <c r="BL30" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="BL30" t="inlineStr"/>
-      <c r="BM30" t="inlineStr">
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="BN30" t="inlineStr">
+      <c r="BO30" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO30" t="inlineStr">
+      <c r="BP30" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP30" t="inlineStr">
+      <c r="BQ30" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ30" t="inlineStr">
+      <c r="BR30" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR30" t="inlineStr">
+      <c r="BS30" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS30" t="inlineStr">
+      <c r="BT30" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT30" t="inlineStr">
+      <c r="BU30" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV30" t="inlineStr">
+      <c r="BV30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW30" t="inlineStr">
         <is>
           <t>alcohol/s13722-022-00345-y (1).pdf</t>
         </is>
@@ -8551,60 +8701,65 @@
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ31" t="inlineStr">
+      <c r="BK31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK31" t="inlineStr">
+      <c r="BL31" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BL31" t="inlineStr"/>
       <c r="BM31" t="inlineStr"/>
-      <c r="BN31" t="inlineStr">
+      <c r="BN31" t="inlineStr"/>
+      <c r="BO31" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO31" t="inlineStr">
+      <c r="BP31" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP31" t="inlineStr">
+      <c r="BQ31" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ31" t="inlineStr">
+      <c r="BR31" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR31" t="inlineStr">
+      <c r="BS31" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS31" t="inlineStr">
+      <c r="BT31" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT31" t="inlineStr">
+      <c r="BU31" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV31" t="inlineStr">
+      <c r="BV31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW31" t="inlineStr">
         <is>
           <t>alcohol/agaf031 (1).pdf</t>
         </is>
@@ -8813,64 +8968,69 @@
       <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ32" t="inlineStr">
+      <c r="BK32" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK32" t="inlineStr">
+      <c r="BL32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BL32" t="inlineStr"/>
-      <c r="BM32" t="inlineStr">
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BN32" t="inlineStr">
+      <c r="BO32" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO32" t="inlineStr">
+      <c r="BP32" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="BP32" t="inlineStr">
+      <c r="BQ32" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ32" t="inlineStr">
+      <c r="BR32" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR32" t="inlineStr">
+      <c r="BS32" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS32" t="inlineStr">
+      <c r="BT32" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT32" t="inlineStr">
+      <c r="BU32" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU32" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV32" t="inlineStr">
+      <c r="BV32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW32" t="inlineStr">
         <is>
           <t>alcohol/qjsa.1970.31.932.pdf</t>
         </is>
@@ -9069,64 +9229,69 @@
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ33" t="inlineStr">
+      <c r="BK33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BK33" t="inlineStr">
+      <c r="BL33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BL33" t="inlineStr">
+      <c r="BM33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BM33" t="inlineStr">
+      <c r="BN33" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="BN33" t="inlineStr">
+      <c r="BO33" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO33" t="inlineStr"/>
-      <c r="BP33" t="inlineStr">
+      <c r="BP33" t="inlineStr"/>
+      <c r="BQ33" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ33" t="inlineStr">
+      <c r="BR33" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR33" t="inlineStr">
+      <c r="BS33" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS33" t="inlineStr">
+      <c r="BT33" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT33" t="inlineStr">
+      <c r="BU33" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV33" t="inlineStr">
+      <c r="BV33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW33" t="inlineStr">
         <is>
           <t>alcohol/jamapsychiatry.2018.3990.pdf</t>
         </is>
